--- a/infra_auto_diag/보고서_양식_Windows.xlsx
+++ b/infra_auto_diag/보고서_양식_Windows.xlsx
@@ -4503,12 +4503,9 @@
       </font>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
+      <font>
+        <color theme="1"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>

--- a/infra_auto_diag/보고서_양식_Windows.xlsx
+++ b/infra_auto_diag/보고서_양식_Windows.xlsx
@@ -4036,13 +4036,7 @@
         <color rgb="FFFFC000"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+    <dxf/>
     <dxf>
       <font>
         <i/>
@@ -4259,13 +4253,7 @@
         <color theme="0" tint="-0.49986266670735802"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+    <dxf/>
     <dxf>
       <font>
         <b/>
@@ -4364,13 +4352,7 @@
         <color rgb="FF0070C0"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+    <dxf/>
     <dxf>
       <font>
         <color theme="0" tint="-0.24994659260841701"/>
